--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.6.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.6.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="96">
-  <si>
-    <t>Загрузочный лист 5.1.6 (Время печати: 27.05.2026 19:51:41)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+  <si>
+    <t>Загрузочный лист 5.1.6 (Время печати: 28.05.2026 17:37:19)</t>
   </si>
   <si>
     <t>Бисёр Маркэт</t>
@@ -190,27 +190,105 @@
     <t>POMPI MINI №-6</t>
   </si>
   <si>
+    <t>G-PM001</t>
+  </si>
+  <si>
+    <t>POMPI MINI №-1</t>
+  </si>
+  <si>
+    <t>G-PM003</t>
+  </si>
+  <si>
+    <t>POMPI MINI №-3</t>
+  </si>
+  <si>
     <t>G-PM004</t>
   </si>
   <si>
     <t>POMPI MINI №-4</t>
   </si>
   <si>
+    <t>G-PM005</t>
+  </si>
+  <si>
+    <t>POMPI MINI №-5</t>
+  </si>
+  <si>
+    <t>GIGA</t>
+  </si>
+  <si>
+    <t>T-0174</t>
+  </si>
+  <si>
+    <t>POMPI GIGA №-5</t>
+  </si>
+  <si>
+    <t>T-0173</t>
+  </si>
+  <si>
+    <t>POMPI GIGA №-4</t>
+  </si>
+  <si>
+    <t>JENSKIY</t>
+  </si>
+  <si>
+    <t>JN-003</t>
+  </si>
+  <si>
+    <t>ZERELLE CLASSIK</t>
+  </si>
+  <si>
+    <t>JN-005</t>
+  </si>
+  <si>
+    <t>LIVIAL NOVA</t>
+  </si>
+  <si>
+    <t>JN-006</t>
+  </si>
+  <si>
+    <t>LIVIAL CLASSIC</t>
+  </si>
+  <si>
+    <t>Ejednevka</t>
+  </si>
+  <si>
+    <t>EJ-001</t>
+  </si>
+  <si>
+    <t>Zerelle (60)</t>
+  </si>
+  <si>
+    <t>EJ-002</t>
+  </si>
+  <si>
+    <t>Zerelle (20)</t>
+  </si>
+  <si>
+    <t>EJ-003</t>
+  </si>
+  <si>
+    <t>Livial (60)</t>
+  </si>
+  <si>
+    <t>EJ-004</t>
+  </si>
+  <si>
+    <t>Livial (20)</t>
+  </si>
+  <si>
+    <t>VLAJNIY</t>
+  </si>
+  <si>
+    <t>VL-004</t>
+  </si>
+  <si>
+    <t>Valajniy 40</t>
+  </si>
+  <si>
     <t>Бонусы</t>
   </si>
   <si>
-    <t>EJ-001</t>
-  </si>
-  <si>
-    <t>Zerelle (60)</t>
-  </si>
-  <si>
-    <t>T-0174</t>
-  </si>
-  <si>
-    <t>POMPI GIGA №-5</t>
-  </si>
-  <si>
     <t>T-0171</t>
   </si>
   <si>
@@ -223,30 +301,6 @@
     <t>ZERELLE NOVA</t>
   </si>
   <si>
-    <t>EJ-002</t>
-  </si>
-  <si>
-    <t>Zerelle (20)</t>
-  </si>
-  <si>
-    <t>EJ-003</t>
-  </si>
-  <si>
-    <t>Livial (60)</t>
-  </si>
-  <si>
-    <t>EJ-004</t>
-  </si>
-  <si>
-    <t>Livial (20)</t>
-  </si>
-  <si>
-    <t>JN-005</t>
-  </si>
-  <si>
-    <t>LIVIAL NOVA</t>
-  </si>
-  <si>
     <t>Общее(вес)</t>
   </si>
   <si>
@@ -262,46 +316,16 @@
     <t>POMPI GIGA №-6</t>
   </si>
   <si>
-    <t>T-0173</t>
-  </si>
-  <si>
-    <t>POMPI GIGA №-4</t>
-  </si>
-  <si>
     <t>T-0172</t>
   </si>
   <si>
     <t>POMPI GIGA №-3</t>
   </si>
   <si>
-    <t>VL-004</t>
-  </si>
-  <si>
-    <t>Valajniy 40</t>
-  </si>
-  <si>
     <t>G-PM002</t>
   </si>
   <si>
     <t>POMPI MINI №-2</t>
-  </si>
-  <si>
-    <t>G-PM003</t>
-  </si>
-  <si>
-    <t>POMPI MINI №-3</t>
-  </si>
-  <si>
-    <t>G-PM005</t>
-  </si>
-  <si>
-    <t>POMPI MINI №-5</t>
-  </si>
-  <si>
-    <t>JN-006</t>
-  </si>
-  <si>
-    <t>LIVIAL CLASSIC</t>
   </si>
 </sst>
 </file>
@@ -813,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AS51"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1349,7 +1373,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="14"/>
       <c r="F8" s="15">
-        <v>204000</v>
+        <v>8</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
@@ -1395,7 +1419,7 @@
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>56</v>
@@ -1408,9 +1432,11 @@
         <v>25500</v>
       </c>
       <c r="F9" s="16">
-        <v>127500</v>
-      </c>
-      <c r="G9" s="16"/>
+        <v>5</v>
+      </c>
+      <c r="G9" s="16">
+        <v>5</v>
+      </c>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -1444,9 +1470,7 @@
       <c r="AL9" s="16"/>
       <c r="AM9" s="16"/>
       <c r="AN9" s="16"/>
-      <c r="AO9" s="16">
-        <v>5</v>
-      </c>
+      <c r="AO9" s="16"/>
       <c r="AP9" s="16"/>
       <c r="AQ9" s="16"/>
       <c r="AR9" s="16"/>
@@ -1456,7 +1480,7 @@
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>58</v>
@@ -1468,9 +1492,7 @@
       <c r="E10" s="16">
         <v>25500</v>
       </c>
-      <c r="F10" s="16">
-        <v>76500</v>
-      </c>
+      <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -1505,9 +1527,7 @@
       <c r="AL10" s="16"/>
       <c r="AM10" s="16"/>
       <c r="AN10" s="16"/>
-      <c r="AO10" s="16">
-        <v>3</v>
-      </c>
+      <c r="AO10" s="16"/>
       <c r="AP10" s="16"/>
       <c r="AQ10" s="16"/>
       <c r="AR10" s="16"/>
@@ -1516,19 +1536,25 @@
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="16"/>
+      <c r="E11" s="16">
+        <v>25500</v>
+      </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="16">
-        <v>1</v>
-      </c>
+      <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
@@ -1567,25 +1593,31 @@
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="E12" s="16">
+        <v>25500</v>
+      </c>
+      <c r="F12" s="16">
+        <v>3</v>
+      </c>
+      <c r="G12" s="16">
+        <v>3</v>
+      </c>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="16">
-        <v>1</v>
-      </c>
-      <c r="L12" s="16">
-        <v>4</v>
-      </c>
-      <c r="M12" s="16">
-        <v>3</v>
-      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
       <c r="P12" s="16"/>
@@ -1595,9 +1627,7 @@
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
       <c r="V12" s="16"/>
-      <c r="W12" s="16">
-        <v>3</v>
-      </c>
+      <c r="W12" s="16"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
@@ -1615,9 +1645,7 @@
       <c r="AL12" s="16"/>
       <c r="AM12" s="16"/>
       <c r="AN12" s="16"/>
-      <c r="AO12" s="16">
-        <v>6</v>
-      </c>
+      <c r="AO12" s="16"/>
       <c r="AP12" s="16"/>
       <c r="AQ12" s="16"/>
       <c r="AR12" s="16"/>
@@ -1626,23 +1654,27 @@
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="A13" s="3">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="16"/>
+      <c r="E13" s="16">
+        <v>25500</v>
+      </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
-      <c r="K13" s="16">
-        <v>1</v>
-      </c>
+      <c r="K13" s="16"/>
       <c r="L13" s="16"/>
-      <c r="M13" s="16">
-        <v>3</v>
-      </c>
+      <c r="M13" s="16"/>
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
       <c r="P13" s="16"/>
@@ -1652,9 +1684,7 @@
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="16"/>
-      <c r="W13" s="16">
-        <v>3</v>
-      </c>
+      <c r="W13" s="16"/>
       <c r="X13" s="16"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
@@ -1672,9 +1702,7 @@
       <c r="AL13" s="16"/>
       <c r="AM13" s="16"/>
       <c r="AN13" s="16"/>
-      <c r="AO13" s="16">
-        <v>6</v>
-      </c>
+      <c r="AO13" s="16"/>
       <c r="AP13" s="16"/>
       <c r="AQ13" s="16"/>
       <c r="AR13" s="16"/>
@@ -1685,7 +1713,9 @@
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="12"/>
+      <c r="C14" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D14" s="13"/>
       <c r="E14" s="14"/>
       <c r="F14" s="15"/>
@@ -1732,11 +1762,19 @@
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="A15" s="3">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="16"/>
+      <c r="E15" s="16">
+        <v>96000</v>
+      </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
@@ -1752,12 +1790,8 @@
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
-      <c r="U15" s="16">
-        <v>2</v>
-      </c>
-      <c r="V15" s="16">
-        <v>3</v>
-      </c>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
       <c r="W15" s="16"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
@@ -1785,20 +1819,26 @@
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="3">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="16"/>
+      <c r="E16" s="16">
+        <v>96000</v>
+      </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="16">
-        <v>2</v>
-      </c>
+      <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
@@ -1807,12 +1847,8 @@
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
-      <c r="U16" s="16">
-        <v>2</v>
-      </c>
-      <c r="V16" s="16">
-        <v>1</v>
-      </c>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
       <c r="W16" s="16"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
@@ -1820,9 +1856,7 @@
       <c r="AA16" s="16"/>
       <c r="AB16" s="16"/>
       <c r="AC16" s="16"/>
-      <c r="AD16" s="16">
-        <v>4</v>
-      </c>
+      <c r="AD16" s="16"/>
       <c r="AE16" s="16"/>
       <c r="AF16" s="16"/>
       <c r="AG16" s="16"/>
@@ -1844,7 +1878,9 @@
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="12" t="s">
+        <v>71</v>
+      </c>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="F17" s="15"/>
@@ -1891,11 +1927,19 @@
       </c>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="3">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16">
+        <v>13800</v>
+      </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
@@ -1904,9 +1948,7 @@
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-      <c r="N18" s="16">
-        <v>15</v>
-      </c>
+      <c r="N18" s="16"/>
       <c r="O18" s="16"/>
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
@@ -1916,35 +1958,25 @@
       <c r="U18" s="16"/>
       <c r="V18" s="16"/>
       <c r="W18" s="16"/>
-      <c r="X18" s="16">
-        <v>6</v>
-      </c>
+      <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
       <c r="AA18" s="16"/>
       <c r="AB18" s="16"/>
       <c r="AC18" s="16"/>
       <c r="AD18" s="16"/>
-      <c r="AE18" s="16">
-        <v>15</v>
-      </c>
+      <c r="AE18" s="16"/>
       <c r="AF18" s="16"/>
       <c r="AG18" s="16"/>
-      <c r="AH18" s="16">
-        <v>9</v>
-      </c>
+      <c r="AH18" s="16"/>
       <c r="AI18" s="16"/>
       <c r="AJ18" s="16"/>
-      <c r="AK18" s="16">
-        <v>12</v>
-      </c>
+      <c r="AK18" s="16"/>
       <c r="AL18" s="16"/>
       <c r="AM18" s="16"/>
       <c r="AN18" s="16"/>
       <c r="AO18" s="16"/>
-      <c r="AP18" s="16">
-        <v>9</v>
-      </c>
+      <c r="AP18" s="16"/>
       <c r="AQ18" s="16"/>
       <c r="AR18" s="16"/>
       <c r="AS18" s="16">
@@ -1952,11 +1984,19 @@
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="A19" s="3">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="D19" s="4"/>
-      <c r="E19" s="16"/>
+      <c r="E19" s="16">
+        <v>12900</v>
+      </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
@@ -1970,9 +2010,7 @@
       <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="16"/>
-      <c r="S19" s="16">
-        <v>24</v>
-      </c>
+      <c r="S19" s="16"/>
       <c r="T19" s="16"/>
       <c r="U19" s="16"/>
       <c r="V19" s="16"/>
@@ -2003,94 +2041,56 @@
       </c>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="A20" s="3">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D20" s="4"/>
-      <c r="E20" s="16"/>
+      <c r="E20" s="16">
+        <v>12900</v>
+      </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
-      <c r="I20" s="16">
-        <v>15</v>
-      </c>
-      <c r="J20" s="16">
-        <v>30</v>
-      </c>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
-      <c r="M20" s="16">
-        <v>6</v>
-      </c>
+      <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="16">
-        <v>9</v>
-      </c>
+      <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
-      <c r="R20" s="16">
-        <v>12</v>
-      </c>
-      <c r="S20" s="16">
-        <v>24</v>
-      </c>
-      <c r="T20" s="16">
-        <v>12</v>
-      </c>
-      <c r="U20" s="16">
-        <v>15</v>
-      </c>
-      <c r="V20" s="16">
-        <v>12</v>
-      </c>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
       <c r="W20" s="16"/>
-      <c r="X20" s="16">
-        <v>6</v>
-      </c>
+      <c r="X20" s="16"/>
       <c r="Y20" s="16"/>
-      <c r="Z20" s="16">
-        <v>15</v>
-      </c>
-      <c r="AA20" s="16">
-        <v>12</v>
-      </c>
-      <c r="AB20" s="16">
-        <v>15</v>
-      </c>
-      <c r="AC20" s="16">
-        <v>21</v>
-      </c>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
       <c r="AD20" s="16"/>
       <c r="AE20" s="16"/>
-      <c r="AF20" s="16">
-        <v>9</v>
-      </c>
-      <c r="AG20" s="16">
-        <v>6</v>
-      </c>
-      <c r="AH20" s="16">
-        <v>9</v>
-      </c>
-      <c r="AI20" s="16">
-        <v>15</v>
-      </c>
-      <c r="AJ20" s="16">
-        <v>60</v>
-      </c>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
       <c r="AK20" s="16"/>
-      <c r="AL20" s="16">
-        <v>6</v>
-      </c>
-      <c r="AM20" s="16">
-        <v>15</v>
-      </c>
-      <c r="AN20" s="16">
-        <v>30</v>
-      </c>
+      <c r="AL20" s="16"/>
+      <c r="AM20" s="16"/>
+      <c r="AN20" s="16"/>
       <c r="AO20" s="16"/>
-      <c r="AP20" s="16">
-        <v>9</v>
-      </c>
+      <c r="AP20" s="16"/>
       <c r="AQ20" s="16"/>
       <c r="AR20" s="16"/>
       <c r="AS20" s="16">
@@ -2100,7 +2100,9 @@
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="12"/>
+      <c r="C21" s="12" t="s">
+        <v>78</v>
+      </c>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
@@ -2147,11 +2149,19 @@
       </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="3">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="16"/>
+      <c r="E22" s="16">
+        <v>27500</v>
+      </c>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
@@ -2159,15 +2169,11 @@
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
-      <c r="M22" s="16">
-        <v>4</v>
-      </c>
+      <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
-      <c r="Q22" s="16">
-        <v>24</v>
-      </c>
+      <c r="Q22" s="16"/>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
@@ -2175,16 +2181,12 @@
       <c r="V22" s="16"/>
       <c r="W22" s="16"/>
       <c r="X22" s="16"/>
-      <c r="Y22" s="16">
-        <v>3</v>
-      </c>
+      <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
       <c r="AA22" s="16"/>
       <c r="AB22" s="16"/>
       <c r="AC22" s="16"/>
-      <c r="AD22" s="16">
-        <v>12</v>
-      </c>
+      <c r="AD22" s="16"/>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16"/>
       <c r="AG22" s="16"/>
@@ -2204,11 +2206,19 @@
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="A23" s="3">
+        <v>16</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D23" s="4"/>
-      <c r="E23" s="16"/>
+      <c r="E23" s="16">
+        <v>11000</v>
+      </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
@@ -2216,15 +2226,11 @@
       <c r="J23" s="16"/>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
-      <c r="M23" s="16">
-        <v>4</v>
-      </c>
+      <c r="M23" s="16"/>
       <c r="N23" s="16"/>
       <c r="O23" s="16"/>
       <c r="P23" s="16"/>
-      <c r="Q23" s="16">
-        <v>48</v>
-      </c>
+      <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
@@ -2232,9 +2238,7 @@
       <c r="V23" s="16"/>
       <c r="W23" s="16"/>
       <c r="X23" s="16"/>
-      <c r="Y23" s="16">
-        <v>3</v>
-      </c>
+      <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="16"/>
@@ -2259,11 +2263,19 @@
       </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="A24" s="3">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="D24" s="4"/>
-      <c r="E24" s="16"/>
+      <c r="E24" s="16">
+        <v>25600</v>
+      </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
@@ -2275,9 +2287,7 @@
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
       <c r="P24" s="16"/>
-      <c r="Q24" s="16">
-        <v>25</v>
-      </c>
+      <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
@@ -2310,11 +2320,19 @@
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="A25" s="3">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="16"/>
+      <c r="E25" s="16">
+        <v>9800</v>
+      </c>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
@@ -2326,20 +2344,14 @@
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
-      <c r="Q25" s="16">
-        <v>50</v>
-      </c>
-      <c r="R25" s="16">
-        <v>5</v>
-      </c>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
       <c r="U25" s="16"/>
       <c r="V25" s="16"/>
       <c r="W25" s="16"/>
-      <c r="X25" s="16">
-        <v>5</v>
-      </c>
+      <c r="X25" s="16"/>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
       <c r="AA25" s="16"/>
@@ -2367,7 +2379,9 @@
     <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="12"/>
+      <c r="C26" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="15"/>
@@ -2414,11 +2428,19 @@
       </c>
     </row>
     <row r="27" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="3">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="D27" s="4"/>
-      <c r="E27" s="16"/>
+      <c r="E27" s="16">
+        <v>3500</v>
+      </c>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
@@ -2457,18 +2479,16 @@
       <c r="AO27" s="16"/>
       <c r="AP27" s="16"/>
       <c r="AQ27" s="16"/>
-      <c r="AR27" s="16">
-        <v>32</v>
-      </c>
+      <c r="AR27" s="16"/>
       <c r="AS27" s="16">
         <v>112000</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="17" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="19"/>
@@ -2513,36 +2533,30 @@
       <c r="AR28" s="19"/>
       <c r="AS28" s="19"/>
     </row>
-    <row r="29" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="16">
-        <v>10</v>
-      </c>
+      <c r="F29" s="16"/>
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="16"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
-      <c r="M29" s="16">
-        <v>1</v>
-      </c>
+      <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
-      <c r="Q29" s="16">
-        <v>6</v>
-      </c>
+      <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
@@ -2555,9 +2569,7 @@
       <c r="AA29" s="16"/>
       <c r="AB29" s="16"/>
       <c r="AC29" s="16"/>
-      <c r="AD29" s="16">
-        <v>3</v>
-      </c>
+      <c r="AD29" s="16"/>
       <c r="AE29" s="16"/>
       <c r="AF29" s="16"/>
       <c r="AG29" s="16"/>
@@ -2576,21 +2588,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="16">
-        <v>2</v>
-      </c>
+      <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
@@ -2605,9 +2615,7 @@
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
-      <c r="U30" s="16">
-        <v>1</v>
-      </c>
+      <c r="U30" s="16"/>
       <c r="V30" s="16"/>
       <c r="W30" s="16"/>
       <c r="X30" s="16"/>
@@ -2616,9 +2624,7 @@
       <c r="AA30" s="16"/>
       <c r="AB30" s="16"/>
       <c r="AC30" s="16"/>
-      <c r="AD30" s="16">
-        <v>1</v>
-      </c>
+      <c r="AD30" s="16"/>
       <c r="AE30" s="16"/>
       <c r="AF30" s="16"/>
       <c r="AG30" s="16"/>
@@ -2637,21 +2643,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>3</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="16">
-        <v>1</v>
-      </c>
+      <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
@@ -2667,9 +2671,7 @@
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
       <c r="U31" s="16"/>
-      <c r="V31" s="16">
-        <v>1</v>
-      </c>
+      <c r="V31" s="16"/>
       <c r="W31" s="16"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
@@ -2696,33 +2698,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>4</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="16">
-        <v>24</v>
-      </c>
+      <c r="F32" s="16"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
-      <c r="L32" s="16">
-        <v>2</v>
-      </c>
+      <c r="L32" s="16"/>
       <c r="M32" s="16"/>
-      <c r="N32" s="16">
-        <v>5</v>
-      </c>
+      <c r="N32" s="16"/>
       <c r="O32" s="16"/>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
@@ -2732,71 +2728,55 @@
       <c r="U32" s="16"/>
       <c r="V32" s="16"/>
       <c r="W32" s="16"/>
-      <c r="X32" s="16">
-        <v>2</v>
-      </c>
+      <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
       <c r="AA32" s="16"/>
       <c r="AB32" s="16"/>
       <c r="AC32" s="16"/>
       <c r="AD32" s="16"/>
-      <c r="AE32" s="16">
-        <v>5</v>
-      </c>
+      <c r="AE32" s="16"/>
       <c r="AF32" s="16"/>
       <c r="AG32" s="16"/>
-      <c r="AH32" s="16">
-        <v>3</v>
-      </c>
+      <c r="AH32" s="16"/>
       <c r="AI32" s="16"/>
       <c r="AJ32" s="16"/>
-      <c r="AK32" s="16">
-        <v>4</v>
-      </c>
+      <c r="AK32" s="16"/>
       <c r="AL32" s="16"/>
       <c r="AM32" s="16"/>
       <c r="AN32" s="16"/>
       <c r="AO32" s="16"/>
-      <c r="AP32" s="16">
-        <v>3</v>
-      </c>
+      <c r="AP32" s="16"/>
       <c r="AQ32" s="16"/>
       <c r="AR32" s="16"/>
       <c r="AS32" s="16">
         <v>24</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>5</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="16">
-        <v>13</v>
-      </c>
+      <c r="F33" s="16"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
       <c r="I33" s="16"/>
       <c r="J33" s="16"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
-      <c r="M33" s="16">
-        <v>1</v>
-      </c>
+      <c r="M33" s="16"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
-      <c r="Q33" s="16">
-        <v>12</v>
-      </c>
+      <c r="Q33" s="16"/>
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
@@ -2828,21 +2808,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>6</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="16">
-        <v>5</v>
-      </c>
+      <c r="F34" s="16"/>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
@@ -2853,9 +2831,7 @@
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
       <c r="P34" s="16"/>
-      <c r="Q34" s="16">
-        <v>5</v>
-      </c>
+      <c r="Q34" s="16"/>
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -2887,21 +2863,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="16">
-        <v>12</v>
-      </c>
+      <c r="F35" s="16"/>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
       <c r="I35" s="16"/>
@@ -2912,20 +2886,14 @@
       <c r="N35" s="16"/>
       <c r="O35" s="16"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="16">
-        <v>10</v>
-      </c>
-      <c r="R35" s="16">
-        <v>1</v>
-      </c>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
       <c r="U35" s="16"/>
       <c r="V35" s="16"/>
       <c r="W35" s="16"/>
-      <c r="X35" s="16">
-        <v>1</v>
-      </c>
+      <c r="X35" s="16"/>
       <c r="Y35" s="16"/>
       <c r="Z35" s="16"/>
       <c r="AA35" s="16"/>
@@ -2950,116 +2918,66 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="16">
-        <v>133</v>
-      </c>
-      <c r="G36" s="16">
-        <v>4</v>
-      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
       <c r="H36" s="16"/>
-      <c r="I36" s="16">
-        <v>5</v>
-      </c>
-      <c r="J36" s="16">
-        <v>10</v>
-      </c>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
-      <c r="M36" s="16">
-        <v>2</v>
-      </c>
+      <c r="M36" s="16"/>
       <c r="N36" s="16"/>
       <c r="O36" s="16"/>
-      <c r="P36" s="16">
-        <v>3</v>
-      </c>
+      <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
-      <c r="R36" s="16">
-        <v>4</v>
-      </c>
-      <c r="S36" s="16">
-        <v>16</v>
-      </c>
-      <c r="T36" s="16">
-        <v>4</v>
-      </c>
-      <c r="U36" s="16">
-        <v>5</v>
-      </c>
-      <c r="V36" s="16">
-        <v>4</v>
-      </c>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
       <c r="W36" s="16"/>
-      <c r="X36" s="16">
-        <v>2</v>
-      </c>
+      <c r="X36" s="16"/>
       <c r="Y36" s="16"/>
-      <c r="Z36" s="16">
-        <v>5</v>
-      </c>
-      <c r="AA36" s="16">
-        <v>4</v>
-      </c>
-      <c r="AB36" s="16">
-        <v>5</v>
-      </c>
-      <c r="AC36" s="16">
-        <v>7</v>
-      </c>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="16"/>
+      <c r="AC36" s="16"/>
       <c r="AD36" s="16"/>
       <c r="AE36" s="16"/>
-      <c r="AF36" s="16">
-        <v>3</v>
-      </c>
-      <c r="AG36" s="16">
-        <v>2</v>
-      </c>
-      <c r="AH36" s="16">
-        <v>3</v>
-      </c>
-      <c r="AI36" s="16">
-        <v>5</v>
-      </c>
-      <c r="AJ36" s="16">
-        <v>20</v>
-      </c>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="16"/>
+      <c r="AI36" s="16"/>
+      <c r="AJ36" s="16"/>
       <c r="AK36" s="16"/>
-      <c r="AL36" s="16">
-        <v>2</v>
-      </c>
-      <c r="AM36" s="16">
-        <v>5</v>
-      </c>
-      <c r="AN36" s="16">
-        <v>10</v>
-      </c>
+      <c r="AL36" s="16"/>
+      <c r="AM36" s="16"/>
+      <c r="AN36" s="16"/>
       <c r="AO36" s="16"/>
-      <c r="AP36" s="16">
-        <v>3</v>
-      </c>
+      <c r="AP36" s="16"/>
       <c r="AQ36" s="16"/>
       <c r="AR36" s="16"/>
       <c r="AS36" s="16">
         <v>133</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="22">
@@ -3182,15 +3100,15 @@
       </c>
       <c r="AS37" s="25"/>
     </row>
-    <row r="38" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="22">
-        <v>204000</v>
+        <v>11676900</v>
       </c>
       <c r="F38" s="26"/>
       <c r="G38" s="27">
@@ -3305,11 +3223,11 @@
       </c>
       <c r="AS38" s="3"/>
     </row>
-    <row r="39" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="17" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="28"/>
@@ -3354,29 +3272,25 @@
       <c r="AR39" s="28"/>
       <c r="AS39" s="19"/>
     </row>
-    <row r="40" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>1</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>4</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3">
-        <v>2</v>
-      </c>
+      <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -3407,29 +3321,25 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
-      <c r="AQ40" s="3">
-        <v>2</v>
-      </c>
+      <c r="AQ40" s="3"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="3">
         <v>384000</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -3466,29 +3376,25 @@
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
-      <c r="AQ41" s="3">
-        <v>1</v>
-      </c>
+      <c r="AQ41" s="3"/>
       <c r="AR41" s="3"/>
       <c r="AS41" s="3">
         <v>96000</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>2</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -3525,29 +3431,25 @@
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
-      <c r="AQ42" s="3">
-        <v>2</v>
-      </c>
+      <c r="AQ42" s="3"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="3">
         <v>192000</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>4</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>1</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -3584,37 +3486,31 @@
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
-      <c r="AQ43" s="3">
-        <v>1</v>
-      </c>
+      <c r="AQ43" s="3"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>5</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3">
-        <v>1</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>1</v>
-      </c>
+      <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
@@ -3651,21 +3547,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>6</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="3">
-        <v>19</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -3702,29 +3596,25 @@
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
-      <c r="AQ45" s="3">
-        <v>19</v>
-      </c>
+      <c r="AQ45" s="3"/>
       <c r="AR45" s="3"/>
       <c r="AS45" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>7</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3">
-        <v>2</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -3761,29 +3651,25 @@
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
-      <c r="AQ46" s="3">
-        <v>2</v>
-      </c>
+      <c r="AQ46" s="3"/>
       <c r="AR46" s="3"/>
       <c r="AS46" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>8</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="3">
-        <v>2</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -3820,29 +3706,25 @@
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
-      <c r="AQ47" s="3">
-        <v>2</v>
-      </c>
+      <c r="AQ47" s="3"/>
       <c r="AR47" s="3"/>
       <c r="AS47" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>9</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="3">
-        <v>1</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -3879,29 +3761,25 @@
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
-      <c r="AQ48" s="3">
-        <v>1</v>
-      </c>
+      <c r="AQ48" s="3"/>
       <c r="AR48" s="3"/>
       <c r="AS48" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>10</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="3">
-        <v>1</v>
-      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -3938,42 +3816,34 @@
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
-      <c r="AQ49" s="3">
-        <v>1</v>
-      </c>
+      <c r="AQ49" s="3"/>
       <c r="AR49" s="3"/>
       <c r="AS49" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>11</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3">
-        <v>21</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-      <c r="L50" s="3">
-        <v>1</v>
-      </c>
+      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="3">
-        <v>20</v>
-      </c>
+      <c r="O50" s="3"/>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
@@ -4007,21 +3877,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>12</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="3">
-        <v>60</v>
-      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -4030,9 +3898,7 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
-      <c r="O51" s="3">
-        <v>60</v>
-      </c>
+      <c r="O51" s="3"/>
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
@@ -4168,6 +4034,6 @@
     <mergeCell ref="C51:D51"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>